--- a/isms-core-framework/A.8-technological-controls/isms-a.8.2-3-5-authentication-privileged-access/WKBK/90_workbooks/ISMS-IMP-A.8.2-3-5.S3_Privileged_Accounts_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.2-3-5-authentication-privileged-access/WKBK/90_workbooks/ISMS-IMP-A.8.2-3-5.S3_Privileged_Accounts_20260208.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:49</t>
+          <t>08.02.2026 12:26</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>• Systems: Domain Controllers, Azure AD tenant, AWS Organization root, PKI CA, SIEM, PAM vault, Backup infrastructure</t>
+          <t>• Systems: Domain Controllers, Microsoft Entra ID (formerly Azure AD) tenant, AWS Organization root, PKI CA, SIEM, PAM vault, Backup infrastructure</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Azure AD Tenant</t>
+          <t>Microsoft Entra ID (formerly Azure AD) Tenant</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
